--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554333419</v>
+        <v>46157.93110085453</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110085453</v>
+        <v>46157.9313432953</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313432953</v>
+        <v>46157.93382082386</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93382082386</v>
+        <v>46157.93693577209</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93693577209</v>
+        <v>46158.28204048604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204048604</v>
+        <v>46158.29650868352</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650868352</v>
+        <v>46158.29805632809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805632809</v>
+        <v>46158.3336879037</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3336879037</v>
+        <v>46158.37220581097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220581097</v>
+        <v>46158.37274612602</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
